--- a/data/liaison_matiere_fournisseur.xlsx
+++ b/data/liaison_matiere_fournisseur.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/58830f9fc3ba735f/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\israc\OneDrive\Documents\pilotage-stock-production\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{E3637B74-6B1B-4C10-858F-E626B336DC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEE45303-013B-4EB8-A213-FAD25816E662}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9558FF14-C606-47E4-A128-97B62FC3603F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Liaison" sheetId="1" r:id="rId1"/>
+    <sheet name="Liaison matiere_ fournisseurs" sheetId="1" r:id="rId1"/>
     <sheet name="ListeFournisseurs" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -843,10 +843,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
